--- a/artfynd/A 19292-2021 artfynd.xlsx
+++ b/artfynd/A 19292-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129954835</v>
       </c>
       <c r="B2" t="n">
-        <v>58456</v>
+        <v>58459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129955019</v>
       </c>
       <c r="B3" t="n">
-        <v>58067</v>
+        <v>58070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129954738</v>
       </c>
       <c r="B4" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19292-2021 artfynd.xlsx
+++ b/artfynd/A 19292-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129954835</v>
       </c>
       <c r="B2" t="n">
-        <v>58459</v>
+        <v>58460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129955019</v>
       </c>
       <c r="B3" t="n">
-        <v>58070</v>
+        <v>58071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129954738</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19292-2021 artfynd.xlsx
+++ b/artfynd/A 19292-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129954835</v>
       </c>
       <c r="B2" t="n">
-        <v>58461</v>
+        <v>58546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129955019</v>
       </c>
       <c r="B3" t="n">
-        <v>58072</v>
+        <v>58157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129954738</v>
       </c>
       <c r="B4" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
